--- a/data/Social_Affordable_data.xlsx
+++ b/data/Social_Affordable_data.xlsx
@@ -658,8 +658,8 @@
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
